--- a/task-reviews/tables/task_tables_readout_subset_value/task_tables_readout_subset_value.xlsx
+++ b/task-reviews/tables/task_tables_readout_subset_value/task_tables_readout_subset_value.xlsx
@@ -4285,7 +4285,711 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the absolute difference between the value from row Phio, column Dist and the value from row Wenn, column Mass.
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Determine the absolute gap between the cells for row Abra under Rank and row Gunn under Age.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Determine the absolute gap between the cells for row Abra under Rank and row Gunn under Age.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 491.273, 647.232, 539.636], [406.464, 104.364, 526.848, 152.727]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 491.273, 647.232, 539.636], [406.464, 104.364, 526.848, 152.727]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>262326103539138</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0024.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="196.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. What is the non-negative difference between the Time entry for Swec and the Gain entry for Swec?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. What is the non-negative difference between the Time entry for Swec and the Gain entry for Swec?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 208.0, 436.56, 284.0], [737.52, 208.0, 888.0, 284.0]], "answer": 25}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 208.0, 436.56, 284.0], [737.52, 208.0, 888.0, 284.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>576264462369960</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0006.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="196.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the absolute difference between the values in the cells at row Diba, column Rate and row Chae, column Rank?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the absolute difference between the values in the cells at row Diba, column Rate and row Chae, column Rank?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 428.4, 406.464, 481.6], [767.616, 534.8, 888.0, 588.0]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 428.4, 406.464, 481.6], [767.616, 534.8, 888.0, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1139528509248558</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0016.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="196.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Determine the absolute gap between the cells for row Hoye under Time and row Irra under Wins.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Determine the absolute gap between the cells for row Hoye under Time and row Irra under Wins.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 162.4, 767.616, 215.6], [406.464, 534.8, 526.848, 588.0]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 162.4, 767.616, 215.6], [406.464, 534.8, 526.848, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1687483751480651</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0023.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="196.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. What is the non-negative difference between the Cost entry for Ause and the Dist entry for Ause?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. What is the non-negative difference between the Cost entry for Ause and the Dist entry for Ause?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 249.455, 888.0, 297.818], [486.72, 249.455, 687.36, 297.818]], "answer": 15}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 249.455, 888.0, 297.818], [486.72, 249.455, 687.36, 297.818]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1753768691987235</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0001.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="196.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. Read the two cell values at (Uel, Dist) and (Rahr, Rank) and report their absolute difference.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. Read the two cell values at (Uel, Dist) and (Rahr, Rank) and report their absolute difference.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 499.333, 687.36, 588.0], [286.08, 410.667, 486.72, 499.333]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 499.333, 687.36, 588.0], [286.08, 410.667, 486.72, 499.333]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1772720879229777</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0013.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="196.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What is the absolute difference between the values in the cells at row Zoe, column Temp and row Lyn, column Cost?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What is the absolute difference between the values in the cells at row Zoe, column Temp and row Lyn, column Cost?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 284.0, 406.464, 360.0], [647.232, 360.0, 767.616, 436.0]], "answer": 23}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 284.0, 406.464, 360.0], [647.232, 360.0, 767.616, 436.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2300204287145649</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0010.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="196.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Find the absolute difference between the value from row Kolb, column Cost and the value from row Dyke, column Cost.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Find the absolute difference between the value from row Kolb, column Cost and the value from row Dyke, column Cost.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 208.0, 888.0, 284.0], [687.36, 360.0, 888.0, 436.0]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 208.0, 888.0, 284.0], [687.36, 360.0, 888.0, 436.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2316560763813698</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0019.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="196.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What is the absolute difference between the values in the cells at row York, column Gain and row Vito, column Rate?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What is the absolute difference between the values in the cells at row York, column Gain and row Vito, column Rate?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 436.0, 737.52, 512.0], [436.56, 512.0, 587.04, 588.0]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 436.0, 737.52, 512.0], [436.56, 512.0, 587.04, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2373477672793684</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0002.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="196.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Read the two cell values at (Derk, Rate) and (Hyde, Mass) and report their absolute difference.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Read the two cell values at (Derk, Rate) and (Hyde, Mass) and report their absolute difference.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 189.0, 436.56, 255.5], [737.52, 322.0, 888.0, 388.5]], "answer": 12}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 189.0, 436.56, 255.5], [737.52, 322.0, 888.0, 388.5]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2722557891101731</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0005.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="196.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. What is the non-negative difference between the Dist entry for Arri and the Rank entry for Dare?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. What is the non-negative difference between the Dist entry for Arri and the Rank entry for Dare?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[767.616, 109.2, 888.0, 162.4], [647.232, 322.0, 767.616, 375.2]], "answer": 22}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[767.616, 109.2, 888.0, 162.4], [647.232, 322.0, 767.616, 375.2]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>3420428104566318</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0008.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="196.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. What is the non-negative difference between the Mass entry for Nea and the Gain entry for Case?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer field: set "answer" to the exact requested integer result.
@@ -4293,63 +4997,127 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the absolute difference between the value from row Phio, column Dist and the value from row Wenn, column Mass.
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. What is the non-negative difference between the Mass entry for Nea and the Gain entry for Case?
 Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 375.2, 526.848, 428.4], [286.08, 322.0, 406.464, 375.2]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 375.2, 526.848, 428.4], [286.08, 322.0, 406.464, 375.2]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3647603279741557</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0000.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="196.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Determine the absolute gap between the cells for row Leod under Pts and row Leod under Wins.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer format: set "answer" to the exact requested integer result.
 Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Determine the absolute gap between the cells for row Leod under Pts and row Leod under Wins.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 436.0, 486.72, 512.0], [486.72, 284.0, 687.36, 360.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 436.0, 486.72, 512.0], [486.72, 284.0, 687.36, 360.0]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 215.6, 687.36, 268.8], [687.36, 215.6, 888.0, 268.8]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 215.6, 687.36, 268.8], [687.36, 215.6, 888.0, 268.8]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>67148359296822</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0021.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0021.json</t>
+      <c r="K14" t="n">
+        <v>3679292228410550</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0004.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0004.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="196.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="15" ht="196.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>cell_difference_two_abs</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Read the two cell values at (Byrd, Gain) and (Rask, Rate) and report their absolute difference.
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the absolute difference between the value from row Anya, column Dist and the value from row Wina, column Cost.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer rule: set "answer" to the exact requested integer result.
@@ -4357,63 +5125,447 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Read the two cell values at (Byrd, Gain) and (Rask, Rate) and report their absolute difference.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the absolute difference between the value from row Anya, column Dist and the value from row Wina, column Cost.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 255.5, 406.464, 322.0], [526.848, 189.0, 647.232, 255.5]], "answer": 23}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 255.5, 406.464, 322.0], [526.848, 189.0, 647.232, 255.5]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4288857621480301</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0009.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0009.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="196.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Read the two cell values at (Taft, Temp) and (Veal, Pts) and report their absolute difference.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Read the two cell values at (Taft, Temp) and (Veal, Pts) and report their absolute difference.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 189.0, 888.0, 255.5], [286.08, 322.0, 486.72, 388.5]], "answer": 31}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 189.0, 888.0, 255.5], [286.08, 322.0, 486.72, 388.5]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4533416449689343</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0017.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="196.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the absolute gap between the cells for row Fax under Score and row Kev under Rank.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the absolute gap between the cells for row Fax under Score and row Kev under Rank.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 469.778, 888.0, 528.889], [486.72, 410.667, 687.36, 469.778]], "answer": 24}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 469.778, 888.0, 528.889], [486.72, 410.667, 687.36, 469.778]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4580759302589804</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0007.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="196.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the absolute gap between the cells for row Alan under Mass and row Kant under Mass.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the absolute gap between the cells for row Alan under Mass and row Kant under Mass.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[436.56, 491.273, 587.04, 539.636], [436.56, 297.818, 587.04, 346.182]], "answer": 10}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[436.56, 491.273, 587.04, 539.636], [436.56, 297.818, 587.04, 346.182]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>4603274238364028</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0022.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="196.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report the requested value or two-cell result. What is the non-negative difference between the Rate entry for Dag and the Pts entry for Dag?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report the requested value or two-cell result. What is the non-negative difference between the Rate entry for Dag and the Pts entry for Dag?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 388.5, 436.56, 455.0], [737.52, 388.5, 888.0, 455.0]], "answer": 18}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 388.5, 436.56, 455.0], [737.52, 388.5, 888.0, 455.0]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5183027589576125</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0018.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="196.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Find the absolute difference between the value from row Hump, column Mass and the value from row Cleo, column Age.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Find the absolute difference between the value from row Hump, column Mass and the value from row Cleo, column Age.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 534.8, 436.56, 588.0], [587.04, 375.2, 737.52, 428.4]], "answer": 28}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 534.8, 436.56, 588.0], [587.04, 375.2, 737.52, 428.4]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[436.56, 512.0, 587.04, 588.0], [587.04, 284.0, 737.52, 360.0]], "answer": 19}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[436.56, 512.0, 587.04, 588.0], [587.04, 284.0, 737.52, 360.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>964965728310269</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0020.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0020.json</t>
+      <c r="K20" t="n">
+        <v>5499684873986519</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0011.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0011.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="196.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="21" ht="196.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>cell_difference_two_abs</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Read the two cell values at (Alla, Temp) and (Keg, Time) and report their absolute difference.
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. What is the absolute difference between the values in the cells at row Tana, column Time and row Rape, column Dist?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. What is the absolute difference between the values in the cells at row Tana, column Time and row Rape, column Dist?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 144.667, 737.52, 233.333], [737.52, 233.333, 888.0, 322.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 144.667, 737.52, 233.333], [737.52, 233.333, 888.0, 322.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5989144126289207</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0003.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="196.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the absolute gap between the cells for row Joni under Age and row Koss under Age.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer rule: set "answer" to the exact requested integer result.
@@ -4421,63 +5573,127 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Read the two cell values at (Alla, Temp) and (Keg, Time) and report their absolute difference.
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the absolute gap between the cells for row Joni under Age and row Koss under Age.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[406.464, 208.0, 526.848, 284.0], [647.232, 436.0, 767.616, 512.0]], "answer": 4}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[406.464, 208.0, 526.848, 284.0], [647.232, 436.0, 767.616, 512.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 360.0, 526.848, 436.0], [406.464, 208.0, 526.848, 284.0]], "answer": 19}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 360.0, 526.848, 436.0], [406.464, 208.0, 526.848, 284.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1125922926999870</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0003.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0003.json</t>
+      <c r="K22" t="n">
+        <v>6492875901632326</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0015.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0015.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="196.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="23" ht="196.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>cell_difference_two_abs</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the two cell values at (Colp, Age) and (Kotz, Age) and report their absolute difference.
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Determine the absolute gap between the cells for row Etom under Wins and row Er under Wins.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Determine the absolute gap between the cells for row Etom under Wins and row Er under Wins.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":6}</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 201.091, 687.36, 249.455], [486.72, 249.455, 687.36, 297.818]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 201.091, 687.36, 249.455], [486.72, 249.455, 687.36, 297.818]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>6545259568366577</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0021.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="196.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>cell_difference_two_abs</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the two cell values at (Glen, Rate) and (Bray, Pts) and report their absolute difference.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer field: set "answer" to the exact requested integer result.
@@ -4485,63 +5701,63 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the two cell values at (Colp, Age) and (Kotz, Age) and report their absolute difference.
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the two cell values at (Glen, Rate) and (Bray, Pts) and report their absolute difference.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
+Answer field: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 132.0, 687.36, 208.0], [486.72, 284.0, 687.36, 360.0]], "answer": 22}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 132.0, 687.36, 208.0], [486.72, 284.0, 687.36, 360.0]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[436.56, 528.889, 587.04, 588.0], [737.52, 174.222, 888.0, 233.333]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[436.56, 528.889, 587.04, 588.0], [737.52, 174.222, 888.0, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>1387627934216459</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0008.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0008.json</t>
+      <c r="K24" t="n">
+        <v>7476566554196555</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0020.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="196.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="25" ht="196.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>cell_difference_two_abs</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the two cell values at (Hong, Temp) and (Jed, Pts) and report their absolute difference.
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Determine the absolute gap between the cells for row Hiro under Time and row Hiro under Pts.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer format: set "answer" to the exact requested integer result.
@@ -4549,63 +5765,63 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the two cell values at (Hong, Temp) and (Jed, Pts) and report their absolute difference.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Determine the absolute gap between the cells for row Hiro under Time and row Hiro under Pts.
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
+Answer format: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 351.556, 767.616, 410.667], [526.848, 233.333, 647.232, 292.444]], "answer": 31}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 351.556, 767.616, 410.667], [526.848, 233.333, 647.232, 292.444]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 233.333, 647.232, 292.444], [767.616, 233.333, 888.0, 292.444]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 233.333, 647.232, 292.444], [767.616, 233.333, 888.0, 292.444]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>1510048007699320</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0017.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0017.json</t>
+      <c r="K25" t="n">
+        <v>7964959940962955</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0014.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="196.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="26" ht="196.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>cell_difference_two_abs</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the two cell values at (Wing, Rank) and (Kym, Time) and report their absolute difference.
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. What is the absolute difference between the values in the cells at row Buzz, column Dist and row Ress, column Cost?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer format: set "answer" to the exact requested integer result.
@@ -4613,1262 +5829,46 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the two cell values at (Wing, Rank) and (Kym, Time) and report their absolute difference.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. What is the absolute difference between the values in the cells at row Buzz, column Dist and row Ress, column Cost?
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":6}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 428.4, 687.36, 481.6], [286.08, 534.8, 486.72, 588.0]], "answer": 10}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 428.4, 687.36, 481.6], [286.08, 534.8, 486.72, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 233.333, 767.616, 322.0], [526.848, 322.0, 647.232, 410.667]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 233.333, 767.616, 322.0], [526.848, 322.0, 647.232, 410.667]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1918677587182619</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0016.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="196.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the absolute difference between the value from row Coop, column Rate and the value from row Olen, column Rate.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the absolute difference between the value from row Coop, column Rate and the value from row Olen, column Rate.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 436.0, 888.0, 512.0], [767.616, 360.0, 888.0, 436.0]], "answer": 2}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 436.0, 888.0, 512.0], [767.616, 360.0, 888.0, 436.0]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>2426784314430108</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0004.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="196.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. What is the non-negative difference between the Pts entry for Hube and the Temp entry for Hama?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. What is the non-negative difference between the Pts entry for Hube and the Temp entry for Hama?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 174.222, 587.04, 233.333], [286.08, 233.333, 436.56, 292.444]], "answer": 13}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 174.222, 587.04, 233.333], [286.08, 233.333, 436.56, 292.444]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2483243045879031</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0022.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="196.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Determine the absolute gap between the cells for row Ikey under Time and row Ury under Cost.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Determine the absolute gap between the cells for row Ikey under Time and row Ury under Cost.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 469.778, 888.0, 528.889], [526.848, 351.556, 647.232, 410.667]], "answer": 15}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 469.778, 888.0, 528.889], [526.848, 351.556, 647.232, 410.667]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>2631539917175618</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0019.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="196.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What is the non-negative difference between the Rate entry for Roux and the Rank entry for Roux?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What is the non-negative difference between the Rate entry for Roux and the Rank entry for Roux?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 360.0, 737.52, 436.0], [436.56, 360.0, 587.04, 436.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 360.0, 737.52, 436.0], [436.56, 360.0, 587.04, 436.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>3066894797608425</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0018.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="196.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the absolute gap between the cells for row Ber under Gain and row Uta under Gain.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the absolute gap between the cells for row Ber under Gain and row Uta under Gain.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 144.667, 486.72, 233.333], [286.08, 499.333, 486.72, 588.0]], "answer": 28}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 144.667, 486.72, 233.333], [286.08, 499.333, 486.72, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>3068738968965303</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0001.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0001.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="196.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Determine the absolute gap between the cells for row Kehr under Mass and row Red under Wins.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Determine the absolute gap between the cells for row Kehr under Mass and row Red under Wins.
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 491.273, 888.0, 539.636], [406.464, 152.727, 526.848, 201.091]], "answer": 3}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 491.273, 888.0, 539.636], [406.464, 152.727, 526.848, 201.091]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>3702301392697506</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0009.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0009.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="196.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. What is the non-negative difference between the Dist entry for Raab and the Dist entry for Toll?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. What is the non-negative difference between the Dist entry for Raab and the Dist entry for Toll?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 144.667, 486.72, 233.333], [286.08, 410.667, 486.72, 499.333]], "answer": 27}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 144.667, 486.72, 233.333], [286.08, 410.667, 486.72, 499.333]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3710509429584234</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0014.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="196.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Read the two cell values at (Codi, Mass) and (Thin, Temp) and report their absolute difference.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Read the two cell values at (Codi, Mass) and (Thin, Temp) and report their absolute difference.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 174.222, 486.72, 233.333], [486.72, 351.556, 687.36, 410.667]], "answer": 31}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 174.222, 486.72, 233.333], [486.72, 351.556, 687.36, 410.667]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4583913841725385</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0023.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="196.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. What is the absolute difference between the values in the cells at row Tyne, column Wins and row Tyne, column Rate?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. What is the absolute difference between the values in the cells at row Tyne, column Wins and row Tyne, column Rate?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 292.444, 888.0, 351.556], [286.08, 292.444, 486.72, 351.556]], "answer": 20}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 292.444, 888.0, 351.556], [286.08, 292.444, 486.72, 351.556]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4803057058650634</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0012.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="196.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the absolute difference between the values in the cells at row Dud, column Pts and row Kane, column Time?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the absolute difference between the values in the cells at row Dud, column Pts and row Kane, column Time?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 410.667, 737.52, 469.778], [286.08, 174.222, 436.56, 233.333]], "answer": 31}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 410.667, 737.52, 469.778], [286.08, 174.222, 436.56, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>5031614944031450</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0013.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="196.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. What is the absolute difference between the values in the cells at row Zita, column Temp and row Thin, column Pts?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. What is the absolute difference between the values in the cells at row Zita, column Temp and row Thin, column Pts?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 268.8, 436.56, 322.0], [436.56, 481.6, 587.04, 534.8]], "answer": 23}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 268.8, 436.56, 322.0], [436.56, 481.6, 587.04, 534.8]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>5137015041382713</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0024.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="196.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Determine the absolute gap between the cells for row De under Pts and row Lymn under Pts.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Determine the absolute gap between the cells for row De under Pts and row Lymn under Pts.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 455.0, 888.0, 521.5], [687.36, 322.0, 888.0, 388.5]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 455.0, 888.0, 521.5], [687.36, 322.0, 888.0, 388.5]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>5785415416332599</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0006.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="196.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the absolute difference between the values in the cells at row Cook, column Gain and row Ley, column Cost?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the absolute difference between the values in the cells at row Cook, column Gain and row Ley, column Cost?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 436.0, 587.04, 512.0], [737.52, 132.0, 888.0, 208.0]], "answer": 18}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 436.0, 587.04, 512.0], [737.52, 132.0, 888.0, 208.0]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6278773269816061</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0015.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="196.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. What is the non-negative difference between the Score entry for Hak and the Score entry for Gigi?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. What is the non-negative difference between the Score entry for Hak and the Score entry for Gigi?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 346.182, 587.04, 394.545], [436.56, 442.909, 587.04, 491.273]], "answer": 21}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 346.182, 587.04, 394.545], [436.56, 442.909, 587.04, 491.273]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>6369882375711063</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0011.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="196.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the absolute difference between the values in the cells at row Fons, column Wins and row Mori, column Pts?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the absolute difference between the values in the cells at row Fons, column Wins and row Mori, column Pts?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 534.8, 737.52, 588.0], [436.56, 109.2, 587.04, 162.4]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 534.8, 737.52, 588.0], [436.56, 109.2, 587.04, 162.4]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>6428820670305886</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0000.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="196.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the absolute difference between the value from row Uund, column Rate and the value from row High, column Mass.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the absolute difference between the value from row Uund, column Rate and the value from row High, column Mass.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 455.0, 767.616, 521.5], [767.616, 255.5, 888.0, 322.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 455.0, 767.616, 521.5], [767.616, 255.5, 888.0, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>6574913108777172</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0007.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="196.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. What is the absolute difference between the values in the cells at row Omer, column Wins and row Mook, column Dist?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. What is the absolute difference between the values in the cells at row Omer, column Wins and row Mook, column Dist?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 208.0, 888.0, 284.0], [486.72, 360.0, 687.36, 436.0]], "answer": 31}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 208.0, 888.0, 284.0], [486.72, 360.0, 687.36, 436.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>7143334706166420</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0010.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="196.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report the requested value or two-cell result. What is the non-negative difference between the Dist entry for Maro and the Dist entry for Ewan?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report the requested value or two-cell result. What is the non-negative difference between the Dist entry for Maro and the Dist entry for Ewan?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 322.0, 888.0, 410.667], [767.616, 499.333, 888.0, 588.0]], "answer": 24}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 322.0, 888.0, 410.667], [767.616, 499.333, 888.0, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>7352851387349701</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0002.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="196.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>cell_difference_two_abs</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Read the two cell values at (Sada, Gain) and (Maxy, Age) and report their absolute difference.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":6}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Read the two cell values at (Sada, Gain) and (Maxy, Age) and report their absolute difference.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":6}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 436.0, 888.0, 512.0], [286.08, 360.0, 406.464, 436.0]], "answer": 5}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 436.0, 888.0, 512.0], [286.08, 360.0, 406.464, 436.0]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>7653726529484179</v>
+        <v>8410544957440554</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_readout_subset_value/images/cell_difference_two_abs/0005.png</t>
+          <t>tables/task_tables_readout_subset_value/images/cell_difference_two_abs/0012.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_readout_subset_value/data/cell_difference_two_abs/0005.json</t>
+          <t>tables/task_tables_readout_subset_value/data/cell_difference_two_abs/0012.json</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,135 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the value where row Pyne intersects column Time.
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the integer in the Gain column for row Amar.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the integer in the Gain column for row Amar.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 144.667, 406.464, 233.333]], "answer": 21}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 144.667, 406.464, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>97128832911911</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0008.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="196.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. What integer appears at the Mass entry for row Gnni?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. What integer appears at the Mass entry for row Gnni?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 255.5, 737.52, 322.0]], "answer": 20}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 255.5, 737.52, 322.0]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>235432828756687</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0024.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="196.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Determine the value where row Inga intersects column Cost.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer rule: set "answer" to the exact requested integer result.
@@ -5990,63 +6118,383 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the value where row Pyne intersects column Time.
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Determine the value where row Inga intersects column Cost.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[436.56, 410.667, 587.04, 499.333]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[436.56, 410.667, 587.04, 499.333]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>250682820612936</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0006.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="196.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What integer appears at the Rank entry for row On?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What integer appears at the Rank entry for row On?
 Return a valid JSON object with key "answer".
 Answer: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 144.667, 888.0, 233.333]], "answer": 14}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 144.667, 888.0, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 152.727, 737.52, 201.091]], "answer": 13}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 152.727, 737.52, 201.091]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>252144390288170</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0001.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0001.json</t>
+      <c r="K5" t="n">
+        <v>415299342381232</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0011.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0011.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="196.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="6" ht="196.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. What value is in the cell at row Kape and column Rate?
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Determine the value where row Kern intersects column Wins.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Determine the value where row Kern intersects column Wins.
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 499.333, 888.0, 588.0]], "answer": 29}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 499.333, 888.0, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>967034153976437</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0018.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0018.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="196.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Determine the value where row Gone intersects column Dist.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Determine the value where row Gone intersects column Dist.
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 109.2, 888.0, 162.4]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 109.2, 888.0, 162.4]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1056615315634308</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0002.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="196.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Cox under the Mass column. What value does it show?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Cox under the Mass column. What value does it show?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 322.0, 436.56, 410.667]], "answer": 26}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 322.0, 436.56, 410.667]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2121764403479661</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0000.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="196.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Ross intersects column Rank.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Ross intersects column Rank.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 189.0, 647.232, 255.5]], "answer": 27}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 189.0, 647.232, 255.5]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2211144761931135</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0021.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="196.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. What integer appears at the Cost entry for row Link?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer format: set "answer" to the exact requested integer result.
@@ -6054,63 +6502,191 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. What value is in the cell at row Kape and column Rate?
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. What integer appears at the Cost entry for row Link?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
+Answer format: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 189.0, 888.0, 255.5]], "answer": 31}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 189.0, 888.0, 255.5]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 499.333, 888.0, 588.0]], "answer": 32}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 499.333, 888.0, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>350460880164375</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0023.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0023.json</t>
+      <c r="K10" t="n">
+        <v>2341807003881848</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0019.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0019.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="196.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="11" ht="196.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Rye under the Gain column. What value does it show?
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Read the cell for row Jeth under the Mass column. What value does it show?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Read the cell for row Jeth under the Mass column. What value does it show?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 292.444, 526.848, 351.556]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 292.444, 526.848, 351.556]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2525271686042191</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0001.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="196.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the integer in the Mass column for row Waly.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the integer in the Mass column for row Waly.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 322.0, 526.848, 410.667]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 322.0, 526.848, 410.667]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>2667455278487342</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0005.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="196.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Determine the value where row Jay intersects column Rate.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer rule: set "answer" to the exact requested integer result.
@@ -6118,63 +6694,191 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Rye under the Gain column. What value does it show?
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Determine the value where row Jay intersects column Rate.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 499.333, 406.464, 588.0]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 499.333, 406.464, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>2752327131013273</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0013.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0013.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="196.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. What value is in the cell at row Ari and column Age?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. What value is in the cell at row Ari and column Age?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 410.667, 737.52, 499.333]], "answer": 1}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 410.667, 737.52, 499.333]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>3233737137867068</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0003.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="196.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Naji intersects column Age.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Naji intersects column Age.
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 512.0, 888.0, 588.0]], "answer": 17}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 512.0, 888.0, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[767.616, 109.2, 888.0, 162.4]], "answer": 4}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[767.616, 109.2, 888.0, 162.4]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>460664629239634</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0012.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0012.json</t>
+      <c r="K15" t="n">
+        <v>4644009905949623</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0009.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0009.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="196.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="16" ht="196.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Determine the value where row Cox intersects column Age.
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. What value is in the cell at row Hyps and column Time?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer rule: set "answer" to the exact requested integer result.
@@ -6182,63 +6886,127 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Determine the value where row Cox intersects column Age.
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. What value is in the cell at row Hyps and column Time?
 Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
+Answer requirement: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 152.727, 888.0, 201.091]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 152.727, 888.0, 201.091]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[436.56, 360.0, 587.04, 436.0]], "answer": 2}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[436.56, 360.0, 587.04, 436.0]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>594648516272303</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0009.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0009.json</t>
+      <c r="K16" t="n">
+        <v>5580293937646793</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0023.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0023.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="196.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="17" ht="196.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the integer in the Cost column for row Jory.
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Edra under the Dist column. What value does it show?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Edra under the Dist column. What value does it show?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 481.6, 436.56, 534.8]], "answer": 3}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 481.6, 436.56, 534.8]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5789411470228842</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0022.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0022.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="196.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. What value is in the cell at row Syst and column Mass?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer requirement: set "answer" to the exact requested integer result.
@@ -6246,63 +7014,191 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the integer in the Cost column for row Jory.
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. What value is in the cell at row Syst and column Mass?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact requested integer result.
+Answer rule: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 249.455, 406.464, 297.818]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 249.455, 406.464, 297.818]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 388.5, 647.232, 455.0]], "answer": 29}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 388.5, 647.232, 455.0]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>823179257971144</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0019.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0019.json</t>
+      <c r="K18" t="n">
+        <v>6033339928449323</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0010.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0010.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="196.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="19" ht="196.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Determine the value where row Ming intersects column Rate.
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the value where row Tim intersects column Rank.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Determine the value where row Tim intersects column Rank.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 410.667, 647.232, 499.333]], "answer": 27}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 410.667, 647.232, 499.333]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>6288436319457401</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0015.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="196.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. Find the integer in the Wins column for row Hum.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. Find the integer in the Wins column for row Hum.
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 534.8, 767.616, 588.0]], "answer": 27}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 534.8, 767.616, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>6956969655021179</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0004.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0004.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="196.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report the requested value or two-cell result. What integer appears at the Gain entry for row Pru?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer: set "answer" to the exact requested integer result.
@@ -6310,127 +7206,191 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Determine the value where row Ming intersects column Rate.
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the table and report the requested value or two-cell result. What integer appears at the Gain entry for row Pru?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":17}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 174.222, 486.72, 233.333]], "answer": 5}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 174.222, 486.72, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>7005535991840141</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0014.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0014.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="196.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>cell_lookup</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Nomi intersects column Mass.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236]],"answer":17}</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Nomi intersects column Mass.
 Return a valid JSON object with key "answer".
 Answer rule: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 284.0, 737.52, 360.0]], "answer": 20}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 284.0, 737.52, 360.0]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 469.778, 737.52, 528.889]], "answer": 21}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 469.778, 737.52, 528.889]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>1048294319474687</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0024.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0024.json</t>
+      <c r="K22" t="n">
+        <v>7240775806891094</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0012.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0012.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="196.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="23" ht="196.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What integer appears at the Dist entry for row Diaz?
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Craw under the Time column. What value does it show?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer field: set "answer" to the exact requested integer result.
+Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
+Answer requirement: set "answer" to the exact requested integer result.
 Example JSON:
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What integer appears at the Dist entry for row Diaz?
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Craw under the Time column. What value does it show?
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
+Answer: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 428.4, 647.232, 481.6]], "answer": 19}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 428.4, 647.232, 481.6]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[436.56, 521.5, 587.04, 588.0]], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[436.56, 521.5, 587.04, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>1563462740305587</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0020.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0020.json</t>
+      <c r="K23" t="n">
+        <v>8446837563963961</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0016.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0016.json</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="196.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
+    <row r="24" ht="196.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. Read the cell for row Pris under the Score column. What value does it show?
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Bree under the Wins column. What value does it show?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer format: set "answer" to the exact requested integer result.
@@ -6438,63 +7398,63 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. Read the cell for row Pris under the Score column. What value does it show?
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Bree under the Wins column. What value does it show?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
+Answer requirement: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 521.5, 436.56, 588.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 521.5, 436.56, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 442.909, 767.616, 491.273]], "answer": 6}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 442.909, 767.616, 491.273]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>1597433407101775</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0017.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0017.json</t>
+      <c r="K24" t="n">
+        <v>8554232233718609</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0007.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0007.json</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="196.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
+    <row r="25" ht="196.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What integer appears at the Dist entry for row Deck?
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. What value is in the cell at row Min and column Wins?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer: set "answer" to the exact requested integer result.
@@ -6502,383 +7462,63 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What integer appears at the Dist entry for row Deck?
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. What value is in the cell at row Min and column Wins?
 Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact requested integer result.
+Answer rule: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 208.0, 406.464, 284.0]], "answer": 25}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 208.0, 406.464, 284.0]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 249.455, 526.848, 297.818]], "answer": 21}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 249.455, 526.848, 297.818]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>3232006061737027</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0002.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0002.json</t>
+      <c r="K25" t="n">
+        <v>8653285876784770</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0020.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="196.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
+    <row r="26" ht="196.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>cell_lookup</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What integer appears at the Mass entry for row Mari?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What integer appears at the Mass entry for row Mari?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 132.0, 587.04, 208.0]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 132.0, 587.04, 208.0]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>4262170351441349</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0011.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="196.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Determine the value where row Bel intersects column Mass.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Use the table values to evaluate the queried cell expression. Determine the value where row Bel intersects column Mass.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 144.667, 486.72, 233.333]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 144.667, 486.72, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>4648484596957068</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0007.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="196.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Read the cell for row Fein under the Age column. What value does it show?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Read the cell for row Fein under the Age column. What value does it show?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 152.727, 737.52, 201.091]], "answer": 15}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 152.727, 737.52, 201.091]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>4714224840332832</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0000.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="196.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What integer appears at the Rank entry for row Torp?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What integer appears at the Rank entry for row Torp?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 174.222, 888.0, 233.333]], "answer": 21}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 174.222, 888.0, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>4724230715816488</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0016.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="196.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the integer in the Rank column for row Hays.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the integer in the Rank column for row Hays.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 469.778, 888.0, 528.889]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 469.778, 888.0, 528.889]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>4730863616049106</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0013.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="196.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Kee under the Time column. What value does it show?
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Determine the value where row Syd intersects column Pts.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
 Answer requirement: set "answer" to the exact requested integer result.
@@ -6886,686 +7526,46 @@
 {"evidence":[[260,180,372,236]],"answer":17}</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Kee under the Time column. What value does it show?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 534.8, 888.0, 588.0]], "answer": 7}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 534.8, 888.0, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>4987164228002364</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0014.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="196.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Eden intersects column Mass.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Determine the value where row Eden intersects column Mass.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 233.333, 486.72, 292.444]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 233.333, 486.72, 292.444]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>6225769583726777</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0022.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0022.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="196.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What integer appears at the Wins entry for row Ange?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What integer appears at the Wins entry for row Ange?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 233.333, 888.0, 322.0]], "answer": 16}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 233.333, 888.0, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6623626107446052</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0021.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="196.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. Determine the value where row Aube intersects column Score.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. Determine the value where row Aube intersects column Score.
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Determine the value where row Syd intersects column Pts.
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":17}</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 208.0, 486.72, 284.0]], "answer": 1}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 208.0, 486.72, 284.0]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[406.464, 491.273, 526.848, 539.636]], "answer": 23}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[406.464, 491.273, 526.848, 539.636]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>6626873393324227</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0010.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="196.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the integer in the Time column for row Cyn.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the integer in the Time column for row Cyn.
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 410.667, 888.0, 499.333]], "answer": 23}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 410.667, 888.0, 499.333]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>6670299446185227</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0003.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="196.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What integer appears at the Pts entry for row Dogs?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What integer appears at the Pts entry for row Dogs?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 109.2, 888.0, 162.4]], "answer": 32}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 109.2, 888.0, 162.4]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7129732569817998</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0015.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0015.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="196.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Badr under the Wins column. What value does it show?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Badr under the Wins column. What value does it show?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 255.5, 406.464, 322.0]], "answer": 26}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 255.5, 406.464, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7498744155295355</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0006.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0006.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="196.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Sura under the Wins column. What value does it show?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Sura under the Wins column. What value does it show?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 436.0, 647.232, 512.0]], "answer": 12}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 436.0, 647.232, 512.0]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>7584071813146674</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0005.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="196.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Jaf under the Age column. What value does it show?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cell for row Jaf under the Age column. What value does it show?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 539.636, 587.04, 588.0]], "answer": 15}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 539.636, 587.04, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8342583124834375</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0018.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0018.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="196.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Determine the value where row Zak intersects column Score.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Determine the value where row Zak intersects column Score.
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 208.0, 486.72, 284.0]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 208.0, 486.72, 284.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8474585379738529</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0004.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0004.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="196.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>cell_lookup</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Judi under the Pts column. What value does it show?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly one bounding box [x1, y1, x2, y2] for the queried supporting cell.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236]],"answer":17}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Read the cell for row Judi under the Pts column. What value does it show?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":17}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 322.0, 436.56, 388.5]], "answer": 9}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 322.0, 436.56, 388.5]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8964301665485163</v>
+        <v>8863812438596397</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_readout_subset_value/images/cell_lookup/0008.png</t>
+          <t>tables/task_tables_readout_subset_value/images/cell_lookup/0017.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_readout_subset_value/data/cell_lookup/0008.json</t>
+          <t>tables/task_tables_readout_subset_value/data/cell_lookup/0017.json</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,199 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. What is the sum of the values in the cells at row Ulda, column Wins and row Libb, column Mass?
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Add the value from row Seel, column Wins to the value from row Hwu, column Wins. What is the result?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Add the value from row Seel, column Wins to the value from row Hwu, column Wins. What is the result?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 351.556, 436.56, 410.667], [286.08, 292.444, 436.56, 351.556]], "answer": 44}</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 351.556, 436.56, 410.667], [286.08, 292.444, 436.56, 351.556]]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>263998669224074</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0016.png</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0016.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="196.5" customHeight="1">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Ran, column Temp and row Lida, column Rank?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Ran, column Temp and row Lida, column Rank?
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[767.616, 491.273, 888.0, 539.636], [286.08, 104.364, 406.464, 152.727]], "answer": 16}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[[767.616, 491.273, 888.0, 539.636], [286.08, 104.364, 406.464, 152.727]]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>585113356442860</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0002.png</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0002.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="196.5" customHeight="1">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the cells for row Rois under Cost and row Ule under Age. What is their total?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the cells for row Rois under Cost and row Ule under Age. What is their total?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[767.616, 360.0, 888.0, 436.0], [647.232, 436.0, 767.616, 512.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>[[767.616, 360.0, 888.0, 436.0], [647.232, 436.0, 767.616, 512.0]]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>640758927385132</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0007.png</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0007.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="196.5" customHeight="1">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the two cell values at (Nye, Score) and (Huai, Rank) and report their sum.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer: set "answer" to the exact requested integer result.
@@ -7687,63 +7879,127 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. What is the sum of the values in the cells at row Ulda, column Wins and row Libb, column Mass?
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the two cell values at (Nye, Score) and (Huai, Rank) and report their sum.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 322.0, 888.0, 375.2], [286.08, 481.6, 486.72, 534.8]], "answer": 47}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 322.0, 888.0, 375.2], [286.08, 481.6, 486.72, 534.8]]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>935199079831746</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0010.png</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0010.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="196.5" customHeight="1">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Lai, column Cost and row Lai, column Pts?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Lai, column Cost and row Lai, column Pts?
 Return a valid JSON object with key "answer".
 Answer field: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 322.0, 486.72, 388.5], [486.72, 122.5, 687.36, 189.0]], "answer": 60}</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 322.0, 486.72, 388.5], [486.72, 122.5, 687.36, 189.0]]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[647.232, 528.889, 767.616, 588.0], [526.848, 528.889, 647.232, 588.0]], "answer": 47}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>[[647.232, 528.889, 767.616, 588.0], [526.848, 528.889, 647.232, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>1051590047414506</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0009.png</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0009.json</t>
+      <c r="K6" t="n">
+        <v>1078332682444764</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0004.png</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0004.json</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="196.5" customHeight="1">
-      <c r="C3" s="2" t="inlineStr">
+    <row r="7" ht="196.5" customHeight="1">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>cell_sum_two</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Add the value from row Remy, column Temp to the value from row Seow, column Temp. What is the result?
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. What total do you get by adding the Dist entry for Wind and the Rank entry for Wind?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer format: set "answer" to the exact requested integer result.
@@ -7751,63 +8007,319 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. Add the value from row Remy, column Temp to the value from row Seow, column Temp. What is the result?
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. What total do you get by adding the Dist entry for Wind and the Rank entry for Wind?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
+Answer rule: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 539.636, 406.464, 588.0], [286.08, 297.818, 406.464, 346.182]], "answer": 64}</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 539.636, 406.464, 588.0], [286.08, 297.818, 406.464, 346.182]]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 109.2, 888.0, 162.4], [436.56, 109.2, 587.04, 162.4]], "answer": 55}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 109.2, 888.0, 162.4], [436.56, 109.2, 587.04, 162.4]]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>1518397184575508</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0018.png</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0018.json</t>
+      <c r="K7" t="n">
+        <v>1951060536823835</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0013.png</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0013.json</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="196.5" customHeight="1">
-      <c r="C4" s="2" t="inlineStr">
+    <row r="8" ht="196.5" customHeight="1">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>cell_sum_two</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Find the two cell values at (Roi, Cost) and (Uta, Age) and report their sum.
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Eda, column Rank and row Hamo, column Cost?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Eda, column Rank and row Hamo, column Cost?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 388.5, 406.464, 455.0], [406.464, 122.5, 526.848, 189.0]], "answer": 54}</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 388.5, 406.464, 455.0], [406.464, 122.5, 526.848, 189.0]]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2249856234649470</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0024.png</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0024.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="196.5" customHeight="1">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cells for row Burg under Wins and row Goss under Score. What is their total?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Read the cells for row Burg under Wins and row Goss under Score. What is their total?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[526.848, 455.0, 647.232, 521.5], [286.08, 122.5, 406.464, 189.0]], "answer": 8}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>[[526.848, 455.0, 647.232, 521.5], [286.08, 122.5, 406.464, 189.0]]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2393966534026030</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0011.png</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0011.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="196.5" customHeight="1">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Read the cells for row Arvy under Age and row Mall under Dist. What is their total?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Read the cells for row Arvy under Age and row Mall under Dist. What is their total?
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 360.0, 888.0, 436.0], [286.08, 132.0, 486.72, 208.0]], "answer": 17}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 360.0, 888.0, 436.0], [286.08, 132.0, 486.72, 208.0]]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2464859403068330</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0015.png</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0015.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="196.5" customHeight="1">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Find the two cell values at (Borg, Dist) and (Ros, Time) and report their sum.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Find the two cell values at (Borg, Dist) and (Ros, Time) and report their sum.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 499.333, 687.36, 588.0], [687.36, 144.667, 888.0, 233.333]], "answer": 52}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 499.333, 687.36, 588.0], [687.36, 144.667, 888.0, 233.333]]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>2865834805181834</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0019.png</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0019.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="196.5" customHeight="1">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. What is the sum of the values in the cells at row Arch, column Dist and row Fenn, column Wins?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer: set "answer" to the exact requested integer result.
@@ -7815,63 +8327,383 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Find the two cell values at (Roi, Cost) and (Uta, Age) and report their sum.
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Use the table values to evaluate the queried cell expression. What is the sum of the values in the cells at row Arch, column Dist and row Fenn, column Wins?
 Return a valid JSON object with key "answer".
 Answer format: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 292.444, 737.52, 351.556], [286.08, 351.556, 436.56, 410.667]], "answer": 58}</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 292.444, 737.52, 351.556], [286.08, 351.556, 436.56, 410.667]]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[767.616, 233.333, 888.0, 322.0], [526.848, 499.333, 647.232, 588.0]], "answer": 24}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>[[767.616, 233.333, 888.0, 322.0], [526.848, 499.333, 647.232, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>1768935589996893</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0001.png</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0001.json</t>
+      <c r="K12" t="n">
+        <v>3839369145358009</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0014.png</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0014.json</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="196.5" customHeight="1">
-      <c r="C5" s="2" t="inlineStr">
+    <row r="13" ht="196.5" customHeight="1">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>cell_sum_two</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Add the value from row Pish, column Wins to the value from row Earl, column Time. What is the result?
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Evy, column Temp and row Weig, column Mass?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Evy, column Temp and row Weig, column Mass?
+Return a valid JSON object with key "answer".
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 428.4, 486.72, 481.6], [687.36, 534.8, 888.0, 588.0]], "answer": 56}</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 428.4, 486.72, 481.6], [687.36, 534.8, 888.0, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3900237236734718</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0005.png</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0005.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="196.5" customHeight="1">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Find the two cell values at (How, Dist) and (Ehud, Score) and report their sum.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Find the requested integer result from the named row and column entries. Find the two cell values at (How, Dist) and (Ehud, Score) and report their sum.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 360.0, 406.464, 436.0], [767.616, 284.0, 888.0, 360.0]], "answer": 49}</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 360.0, 406.464, 436.0], [767.616, 284.0, 888.0, 360.0]]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>4153583061459597</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0008.png</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0008.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="196.5" customHeight="1">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the two cell values at (Kreg, Gain) and (Kan, Gain) and report their sum.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the two cell values at (Kreg, Gain) and (Kan, Gain) and report their sum.
+Return a valid JSON object with key "answer".
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[486.72, 122.5, 687.36, 189.0], [486.72, 322.0, 687.36, 388.5]], "answer": 42}</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>[[486.72, 122.5, 687.36, 189.0], [486.72, 322.0, 687.36, 388.5]]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>4316697179174415</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0003.png</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0003.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="196.5" customHeight="1">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Read the cells for row Bord under Time and row Tate under Temp. What is their total?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Read the cells for row Bord under Time and row Tate under Temp. What is their total?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 351.556, 436.56, 410.667], [737.52, 410.667, 888.0, 469.778]], "answer": 37}</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 351.556, 436.56, 410.667], [737.52, 410.667, 888.0, 469.778]]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>4345657946470940</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0000.png</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0000.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="196.5" customHeight="1">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. Add the value from row Kate, column Age to the value from row Wynn, column Dist. What is the result?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. Add the value from row Kate, column Age to the value from row Wynn, column Dist. What is the result?
+Return a valid JSON object with key "answer".
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[767.616, 394.545, 888.0, 442.909], [286.08, 297.818, 406.464, 346.182]], "answer": 59}</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>[[767.616, 394.545, 888.0, 442.909], [286.08, 297.818, 406.464, 346.182]]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>4403268944620964</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0021.png</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0021.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="196.5" customHeight="1">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Till, column Age and row Ede, column Rank?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer requirement: set "answer" to the exact requested integer result.
@@ -7879,63 +8711,255 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Add the value from row Pish, column Wins to the value from row Earl, column Time. What is the result?
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Till, column Age and row Ede, column Rank?
 Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
+Answer requirement: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 144.667, 647.232, 233.333], [406.464, 322.0, 526.848, 410.667]], "answer": 32}</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 144.667, 647.232, 233.333], [406.464, 322.0, 526.848, 410.667]]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 491.273, 737.52, 539.636], [436.56, 442.909, 587.04, 491.273]], "answer": 62}</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 491.273, 737.52, 539.636], [436.56, 442.909, 587.04, 491.273]]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>2178118950645976</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0015.png</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0015.json</t>
+      <c r="K18" t="n">
+        <v>4680965179380377</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0012.png</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0012.json</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="196.5" customHeight="1">
-      <c r="C6" s="2" t="inlineStr">
+    <row r="19" ht="196.5" customHeight="1">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>cell_sum_two</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the two cell values at (Syst, Wins) and (Syst, Mass) and report their sum.
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Find the two cell values at (Hara, Mass) and (Pang, Wins) and report their sum.
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer requirement: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Find the two cell values at (Hara, Mass) and (Pang, Wins) and report their sum.
+Return a valid JSON object with key "answer".
+Answer rule: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 410.667, 888.0, 469.778], [286.08, 292.444, 486.72, 351.556]], "answer": 7}</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 410.667, 888.0, 469.778], [286.08, 292.444, 486.72, 351.556]]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>5285766431893009</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0017.png</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0017.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="196.5" customHeight="1">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Read the cells for row Awad under Rank and row Oina under Gain. What is their total?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Read the cells for row Awad under Rank and row Oina under Gain. What is their total?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 322.0, 486.72, 388.5], [486.72, 189.0, 687.36, 255.5]], "answer": 14}</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 322.0, 486.72, 388.5], [486.72, 189.0, 687.36, 255.5]]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>5547363489965350</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0023.png</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0023.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="196.5" customHeight="1">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Rona, column Gain and row Rona, column Cost?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer format: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. What is the sum of the values in the cells at row Rona, column Gain and row Rona, column Cost?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 512.0, 888.0, 588.0], [286.08, 512.0, 486.72, 588.0]], "answer": 63}</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 512.0, 888.0, 588.0], [286.08, 512.0, 486.72, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>6258274131468745</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0006.png</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0006.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="196.5" customHeight="1">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. Find the two cell values at (Edla, Rank) and (Gino, Gain) and report their sum.
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer rule: set "answer" to the exact requested integer result.
@@ -7943,127 +8967,191 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. Find the two cell values at (Syst, Wins) and (Syst, Mass) and report their sum.
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the named table cell or cells and compute the requested result. Find the two cell values at (Edla, Rank) and (Gino, Gain) and report their sum.
 Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
+Answer format: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 233.333, 436.56, 322.0], [737.52, 233.333, 888.0, 322.0]], "answer": 63}</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 233.333, 436.56, 322.0], [737.52, 233.333, 888.0, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[767.616, 322.0, 888.0, 388.5], [526.848, 521.5, 647.232, 588.0]], "answer": 57}</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>[[767.616, 322.0, 888.0, 388.5], [526.848, 521.5, 647.232, 588.0]]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>2965704782231952</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0022.png</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0022.json</t>
+      <c r="K22" t="n">
+        <v>6279137387703766</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0022.png</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0022.json</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="196.5" customHeight="1">
-      <c r="C7" s="2" t="inlineStr">
+    <row r="23" ht="196.5" customHeight="1">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>cell_sum_two</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What total do you get by adding the Wins entry for Hett and the Age entry for Luba?
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Add the value from row Amy, column Cost to the value from row Hamo, column Gain. What is the result?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
+Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer: set "answer" to the exact requested integer result.
 Example JSON:
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What total do you get by adding the Wins entry for Hett and the Age entry for Luba?
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Answer this question. Add the value from row Amy, column Cost to the value from row Hamo, column Gain. What is the result?
 Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
+Answer field: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 499.333, 888.0, 588.0], [406.464, 410.667, 526.848, 499.333]], "answer": 31}</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 499.333, 888.0, 588.0], [406.464, 410.667, 526.848, 499.333]]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[737.52, 436.0, 888.0, 512.0], [436.56, 132.0, 587.04, 208.0]], "answer": 9}</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[[737.52, 436.0, 888.0, 512.0], [436.56, 132.0, 587.04, 208.0]]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>4016921644758208</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0006.png</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0006.json</t>
+      <c r="K23" t="n">
+        <v>7537371627280357</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0018.png</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0018.json</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="196.5" customHeight="1">
-      <c r="C8" s="2" t="inlineStr">
+    <row r="24" ht="196.5" customHeight="1">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>cell_sum_two</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Read the cells for row Tab under Gain and row Elah under Mass. What is their total?
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. What total do you get by adding the Rate entry for Meit and the Rate entry for Vona?
+Return a valid JSON object with keys "evidence" and "answer" in that order.
+Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the named table cell or cells and compute the requested result. What total do you get by adding the Rate entry for Meit and the Rate entry for Vona?
+Return a valid JSON object with key "answer".
+Answer field: set "answer" to the exact requested integer result.
+Example JSON:
+{"answer":29}</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[587.04, 360.0, 737.52, 436.0], [587.04, 208.0, 737.52, 284.0]], "answer": 22}</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>[[587.04, 360.0, 737.52, 436.0], [587.04, 208.0, 737.52, 284.0]]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bbox_set</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>7847123977813905</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0001.png</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="196.5" customHeight="1">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>task_tables_readout_subset_value</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>cell_sum_two</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Read the cells for row Arda under Time and row Bove under Temp. What is their total?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer format: set "answer" to the exact requested integer result.
@@ -8071,255 +9159,63 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. Read the cells for row Tab under Gain and row Elah under Mass. What is their total?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 442.909, 687.36, 491.273], [286.08, 394.545, 486.72, 442.909]], "answer": 11}</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 442.909, 687.36, 491.273], [286.08, 394.545, 486.72, 442.909]]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>4055609761925809</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0014.png</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0014.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="196.5" customHeight="1">
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Add the value from row Pepe, column Pts to the value from row Dobb, column Pts. What is the result?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Answer this question. Add the value from row Pepe, column Pts to the value from row Dobb, column Pts. What is the result?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 284.0, 486.72, 360.0], [286.08, 512.0, 486.72, 588.0]], "answer": 40}</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 284.0, 486.72, 360.0], [286.08, 512.0, 486.72, 588.0]]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>4203617780703076</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0024.png</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0024.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="196.5" customHeight="1">
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Add the value from row Rico, column Temp to the value from row Ezra, column Score. What is the result?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Add the value from row Rico, column Temp to the value from row Ezra, column Score. What is the result?
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[486.72, 455.0, 687.36, 521.5], [687.36, 189.0, 888.0, 255.5]], "answer": 31}</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>[[486.72, 455.0, 687.36, 521.5], [687.36, 189.0, 888.0, 255.5]]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4519649362000499</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0005.png</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0005.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="196.5" customHeight="1">
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the two cell values at (Sami, Mass) and (Tare, Age) and report their sum.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence requirement: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Read the table and report the requested value or two-cell result. Find the two cell values at (Sami, Mass) and (Tare, Age) and report their sum.
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Read the cells for row Arda under Time and row Bove under Temp. What is their total?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[406.464, 109.2, 526.848, 162.4], [767.616, 322.0, 888.0, 375.2]], "answer": 19}</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>[[406.464, 109.2, 526.848, 162.4], [767.616, 322.0, 888.0, 375.2]]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[286.08, 394.545, 406.464, 442.909], [406.464, 152.727, 526.848, 201.091]], "answer": 41}</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>[[286.08, 394.545, 406.464, 442.909], [406.464, 152.727, 526.848, 201.091]]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>4995660314818165</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0008.png</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0008.json</t>
+      <c r="K25" t="n">
+        <v>7871898427171929</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0020.png</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0020.json</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="196.5" customHeight="1">
-      <c r="C12" s="2" t="inlineStr">
+    <row r="26" ht="196.5" customHeight="1">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>task_tables_readout_subset_value</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>cell_sum_two</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Add the value from row Bird, column Dist to the value from row Old, column Pts. What is the result?
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the cells for row Toh under Age and row Rama under Gain. What is their total?
 Return a valid JSON object with keys "evidence" and "answer" in that order.
 Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
 Answer requirement: set "answer" to the exact requested integer result.
@@ -8327,942 +9223,46 @@
 {"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. Add the value from row Bird, column Dist to the value from row Old, column Pts. What is the result?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 255.5, 647.232, 322.0], [406.464, 122.5, 526.848, 189.0]], "answer": 54}</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 255.5, 647.232, 322.0], [406.464, 122.5, 526.848, 189.0]]</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>5295648796835752</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0021.png</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0021.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="196.5" customHeight="1">
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Read the cells for row Lind under Rank and row Ravo under Time. What is their total?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the table and report the requested value or two-cell result. Read the cells for row Lind under Rank and row Ravo under Time. What is their total?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[767.616, 539.636, 888.0, 588.0], [647.232, 346.182, 767.616, 394.545]], "answer": 36}</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>[[767.616, 539.636, 888.0, 588.0], [647.232, 346.182, 767.616, 394.545]]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>5544078284745894</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0016.png</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0016.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="196.5" customHeight="1">
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Read the cells for row Aara under Gain and row Thom under Cost. What is their total?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Look at the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. Read the cells for row Aara under Gain and row Thom under Cost. What is their total?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 255.5, 767.616, 322.0], [526.848, 189.0, 647.232, 255.5]], "answer": 29}</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 255.5, 767.616, 322.0], [526.848, 189.0, 647.232, 255.5]]</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5686259760994833</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0013.png</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0013.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="196.5" customHeight="1">
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Kier, column Mass and row Mok, column Gain?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Kier, column Mass and row Mok, column Gain?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[436.56, 115.111, 587.04, 174.222], [587.04, 410.667, 737.52, 469.778]], "answer": 46}</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>[[436.56, 115.111, 587.04, 174.222], [587.04, 410.667, 737.52, 469.778]]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>6090819879181095</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0023.png</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0023.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="196.5" customHeight="1">
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. What total do you get by adding the Cost entry for Adah and the Wins entry for Uni?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. What total do you get by adding the Cost entry for Adah and the Wins entry for Uni?
-Return a valid JSON object with key "answer".
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[647.232, 394.545, 767.616, 442.909], [526.848, 491.273, 647.232, 539.636]], "answer": 33}</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>[[647.232, 394.545, 767.616, 442.909], [526.848, 491.273, 647.232, 539.636]]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>6766879610114707</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0011.png</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0011.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="196.5" customHeight="1">
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Dan, column Wins and row Dan, column Score?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Dan, column Wins and row Dan, column Score?
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>You are given a table: a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Read the named table cell or cells and compute the requested result. Read the cells for row Toh under Age and row Rama under Gain. What is their total?
 Return a valid JSON object with key "answer".
 Answer requirement: set "answer" to the exact requested integer result.
 Example JSON:
 {"answer":29}</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 322.0, 888.0, 410.667], [286.08, 322.0, 436.56, 410.667]], "answer": 64}</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 322.0, 888.0, 410.667], [286.08, 322.0, 436.56, 410.667]]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>{"evidence": [[687.36, 152.727, 888.0, 201.091], [286.08, 104.364, 486.72, 152.727]], "answer": 36}</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>[[687.36, 152.727, 888.0, 201.091], [286.08, 104.364, 486.72, 152.727]]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>bbox_set</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>6896443413043621</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0010.png</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0010.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="196.5" customHeight="1">
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Find the two cell values at (Orms, Score) and (Rick, Score) and report their sum.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. Find the two cell values at (Orms, Score) and (Rick, Score) and report their sum.
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[737.52, 528.889, 888.0, 588.0], [737.52, 174.222, 888.0, 233.333]], "answer": 32}</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>[[737.52, 528.889, 888.0, 588.0], [737.52, 174.222, 888.0, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>6897066534672703</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0012.png</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0012.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="196.5" customHeight="1">
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the two cell values at (Chil, Pts) and (Tonl, Score) and report their sum.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the two cell values at (Chil, Pts) and (Tonl, Score) and report their sum.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 410.667, 737.52, 499.333], [436.56, 144.667, 587.04, 233.333]], "answer": 60}</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 410.667, 737.52, 499.333], [436.56, 144.667, 587.04, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>7153752809696117</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0019.png</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0019.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="196.5" customHeight="1">
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What total do you get by adding the Gain entry for Zoie and the Gain entry for Byrd?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Use the table values to evaluate the queried cell expression. What total do you get by adding the Gain entry for Zoie and the Gain entry for Byrd?
-Return a valid JSON object with key "answer".
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[587.04, 322.0, 737.52, 375.2], [587.04, 428.4, 737.52, 481.6]], "answer": 27}</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>[[587.04, 322.0, 737.52, 375.2], [587.04, 428.4, 737.52, 481.6]]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>7368499173119192</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0020.png</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0020.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="196.5" customHeight="1">
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. What is the sum of the values in the cells at row Derk, column Time and row Coy, column Time?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a card-style table with one Name column, several numeric columns, a rounded outer frame, and a shaded header row. Read the named table cell or cells and compute the requested result. What is the sum of the values in the cells at row Derk, column Time and row Coy, column Time?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[526.848, 428.4, 647.232, 481.6], [526.848, 268.8, 647.232, 322.0]], "answer": 8}</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[[526.848, 428.4, 647.232, 481.6], [526.848, 268.8, 647.232, 322.0]]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>7432975499187816</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0002.png</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0002.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="196.5" customHeight="1">
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What total do you get by adding the Score entry for Ann and the Mass entry for Bick?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence rule: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a zebra-striped table with one Name column, several numeric columns, alternating row shading, and a shaded header row. Answer this question. What total do you get by adding the Score entry for Ann and the Mass entry for Bick?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 388.5, 436.56, 455.0], [436.56, 122.5, 587.04, 189.0]], "answer": 20}</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 388.5, 436.56, 455.0], [436.56, 122.5, 587.04, 189.0]]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>7811085877994225</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0000.png</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0000.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="196.5" customHeight="1">
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the two cell values at (Kuhn, Time) and (Nona, Temp) and report their sum.
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>The image shows a spreadsheet-style table with one Name column, several numeric columns, full grid lines, and a shaded header row. Use the table values to evaluate the queried cell expression. Find the two cell values at (Kuhn, Time) and (Nona, Temp) and report their sum.
-Return a valid JSON object with key "answer".
-Answer rule: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[687.36, 174.222, 888.0, 233.333], [486.72, 410.667, 687.36, 469.778]], "answer": 58}</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>[[687.36, 174.222, 888.0, 233.333], [486.72, 410.667, 687.36, 469.778]]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>8087581556939107</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0003.png</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0003.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="196.5" customHeight="1">
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Read the cells for row Chan under Rate and row Chan under Wins. What is their total?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Use the table in the image. It shows a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Answer this question. Read the cells for row Chan under Rate and row Chan under Wins. What is their total?
-Return a valid JSON object with key "answer".
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 428.4, 406.464, 481.6], [767.616, 428.4, 888.0, 481.6]], "answer": 36}</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 428.4, 406.464, 481.6], [767.616, 428.4, 888.0, 481.6]]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>8222610954403553</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0017.png</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0017.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="196.5" customHeight="1">
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. What total do you get by adding the Rank entry for Ursi and the Time entry for Ebba?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence field: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer field: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>You are given a table: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Read the table and report the requested value or two-cell result. What total do you get by adding the Rank entry for Ursi and the Time entry for Ebba?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 360.0, 406.464, 436.0], [767.616, 436.0, 888.0, 512.0]], "answer": 14}</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 360.0, 406.464, 436.0], [767.616, 436.0, 888.0, 512.0]]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>8795123517937647</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0007.png</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0007.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="196.5" customHeight="1">
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>task_tables_readout_subset_value</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>cell_sum_two</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Fein, column Mass and row Lymn, column Rank?
-Return a valid JSON object with keys "evidence" and "answer" in that order.
-Evidence format: set "evidence" to an array containing exactly two bounding boxes [x1, y1, x2, y2] in the same order as the two queried cells.
-Answer requirement: set "answer" to the exact requested integer result.
-Example JSON:
-{"evidence":[[260,180,372,236],[374,180,486,236]],"answer":29}</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Work from the styled table shown in the image: a ledger-style table with one Name column, several numeric columns, strong horizontal rules, and minimal vertical separators. Find the requested integer result from the named row and column entries. What is the sum of the values in the cells at row Fein, column Mass and row Lymn, column Rank?
-Return a valid JSON object with key "answer".
-Answer format: set "answer" to the exact requested integer result.
-Example JSON:
-{"answer":29}</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>{"evidence": [[286.08, 322.0, 436.56, 410.667], [737.52, 144.667, 888.0, 233.333]], "answer": 59}</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>[[286.08, 322.0, 436.56, 410.667], [737.52, 144.667, 888.0, 233.333]]</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bbox_set</t>
-        </is>
-      </c>
       <c r="K26" t="n">
-        <v>8886841387978799</v>
+        <v>8167927631399427</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_readout_subset_value/images/cell_sum_two/0004.png</t>
+          <t>tables/task_tables_readout_subset_value/images/cell_sum_two/0009.png</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>task_tables_readout_subset_value/data/cell_sum_two/0004.json</t>
+          <t>tables/task_tables_readout_subset_value/data/cell_sum_two/0009.json</t>
         </is>
       </c>
     </row>
